--- a/data/trans_dic/P14B23-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P14B23-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con enfermedades crónicas discapacitantes de salud mental (trastornos depresivos o ansiedad)</t>
+          <t>Población cuya depresión o ansiedad le limita (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,32</t>
+          <t>1,18; 3,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,16</t>
+          <t>1,0; 3,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,02; 7,74</t>
+          <t>4,04; 7,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,99; 11,25</t>
+          <t>7,12; 11,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,06; 10,44</t>
+          <t>6,07; 10,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,8; 7,9</t>
+          <t>4,86; 7,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,5; 7,04</t>
+          <t>4,38; 6,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,87; 6,26</t>
+          <t>3,78; 6,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,87; 7,24</t>
+          <t>4,95; 7,34</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,05</t>
+          <t>1,79; 4,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,49</t>
+          <t>0,94; 2,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,27</t>
+          <t>1,03; 3,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,68; 10,36</t>
+          <t>6,56; 10,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,74; 7,86</t>
+          <t>4,54; 7,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,94; 8,66</t>
+          <t>5,96; 8,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,64; 6,74</t>
+          <t>4,55; 6,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,04; 4,82</t>
+          <t>3,14; 4,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,0; 5,31</t>
+          <t>2,98; 5,37</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,91</t>
+          <t>1,1; 3,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,72</t>
+          <t>1,46; 3,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 5,25</t>
+          <t>2,13; 5,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,43; 9,26</t>
+          <t>5,46; 9,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,11; 9,14</t>
+          <t>5,18; 9,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,75; 9,96</t>
+          <t>3,36; 9,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,63; 5,87</t>
+          <t>3,77; 5,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,69; 5,85</t>
+          <t>3,65; 5,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,68; 6,94</t>
+          <t>3,72; 7,04</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,01</t>
+          <t>1,82; 4,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,31</t>
+          <t>1,38; 3,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,05; 5,73</t>
+          <t>3,26; 5,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,2; 9,71</t>
+          <t>6,26; 9,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,93; 7,99</t>
+          <t>4,79; 8,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,11; 9,3</t>
+          <t>6,09; 9,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,44; 6,46</t>
+          <t>4,45; 6,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,47; 5,42</t>
+          <t>3,46; 5,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,27; 7,35</t>
+          <t>5,23; 7,3</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,99; 3,15</t>
+          <t>1,98; 3,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,51</t>
+          <t>1,52; 2,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,81; 4,42</t>
+          <t>2,76; 4,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,13; 9,01</t>
+          <t>7,1; 8,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,87; 7,57</t>
+          <t>5,83; 7,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,78; 8,09</t>
+          <t>5,86; 8,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,79; 5,83</t>
+          <t>4,83; 5,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,9; 4,91</t>
+          <t>3,94; 4,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,8; 6,09</t>
+          <t>4,81; 6,15</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con enfermedades crónicas discapacitantes de salud mental (trastornos depresivos o ansiedad)</t>
+          <t>Población cuya depresión o ansiedad le limita (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8256; 23381</t>
+          <t>8310; 23156</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6773; 21304</t>
+          <t>6722; 21740</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25570; 49158</t>
+          <t>25671; 50130</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48579; 78180</t>
+          <t>49482; 79923</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>40786; 70235</t>
+          <t>40864; 70773</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34852; 57305</t>
+          <t>35239; 57467</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>62886; 98378</t>
+          <t>61275; 95350</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>52179; 84336</t>
+          <t>50944; 81757</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>66291; 98524</t>
+          <t>67374; 99841</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19264; 41229</t>
+          <t>18185; 42192</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9939; 25473</t>
+          <t>9624; 26151</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11747; 39012</t>
+          <t>12284; 39686</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>68596; 106365</t>
+          <t>67428; 105326</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>49463; 82025</t>
+          <t>47306; 80991</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>56965; 83042</t>
+          <t>57171; 83692</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>94770; 137847</t>
+          <t>92969; 136389</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>62751; 99552</t>
+          <t>64932; 100113</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>64612; 114218</t>
+          <t>64016; 115546</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8581; 29608</t>
+          <t>8337; 27906</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11107; 28272</t>
+          <t>11067; 28919</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15379; 36994</t>
+          <t>14997; 38443</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>42169; 71842</t>
+          <t>42401; 72264</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>40103; 71745</t>
+          <t>40674; 70819</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35014; 92976</t>
+          <t>31361; 93173</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55663; 89994</t>
+          <t>57891; 91943</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>56930; 90370</t>
+          <t>56315; 89893</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>60346; 113654</t>
+          <t>60923; 115249</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16321; 37935</t>
+          <t>17270; 39142</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12397; 31022</t>
+          <t>12923; 30822</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28242; 53117</t>
+          <t>30176; 53410</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>65038; 101835</t>
+          <t>65657; 101308</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>51486; 83445</t>
+          <t>50043; 84111</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>66936; 101781</t>
+          <t>66696; 104138</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>88644; 128977</t>
+          <t>88828; 130126</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>68750; 107358</t>
+          <t>68464; 105742</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>106560; 148517</t>
+          <t>105713; 147662</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>68163; 107992</t>
+          <t>67656; 107473</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>53009; 85211</t>
+          <t>51745; 84366</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>97311; 153069</t>
+          <t>95568; 151131</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>253008; 319642</t>
+          <t>251793; 317833</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>208193; 268155</t>
+          <t>206790; 268244</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>214393; 300328</t>
+          <t>217540; 301198</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>333642; 406157</t>
+          <t>336930; 414637</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>270864; 340407</t>
+          <t>273416; 340593</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>344408; 437020</t>
+          <t>345309; 440752</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P14B23-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P14B23-Habitat-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,29</t>
+          <t>1,13; 3,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,22</t>
+          <t>1,0; 3,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,04; 7,89</t>
+          <t>4,03; 7,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,12; 11,5</t>
+          <t>6,99; 11,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,07; 10,52</t>
+          <t>5,93; 10,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,86; 7,92</t>
+          <t>5,5; 8,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,38; 6,82</t>
+          <t>4,49; 6,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,78; 6,07</t>
+          <t>3,84; 6,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,95; 7,34</t>
+          <t>5,19; 7,66</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,15</t>
+          <t>1,88; 4,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,56</t>
+          <t>0,99; 2,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,33</t>
+          <t>1,64; 3,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,56; 10,25</t>
+          <t>6,5; 10,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,54; 7,77</t>
+          <t>4,67; 7,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,96; 8,73</t>
+          <t>5,9; 8,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,55; 6,67</t>
+          <t>4,52; 6,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,14; 4,85</t>
+          <t>3,04; 4,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,98; 5,37</t>
+          <t>4,06; 5,7</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,68</t>
+          <t>1,13; 3,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,81</t>
+          <t>1,45; 3,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 5,46</t>
+          <t>2,22; 5,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,46; 9,31</t>
+          <t>5,59; 9,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,18; 9,02</t>
+          <t>5,02; 8,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,36; 9,98</t>
+          <t>7,9; 11,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,77; 5,99</t>
+          <t>3,67; 5,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,65; 5,82</t>
+          <t>3,6; 5,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,72; 7,04</t>
+          <t>5,37; 7,86</t>
         </is>
       </c>
     </row>
@@ -965,37 +965,37 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7,76%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6,39%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8,49%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,38%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4,38%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7,76%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,39%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,81%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,38%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4,38%</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,13</t>
+          <t>1,8; 4,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,29</t>
+          <t>1,36; 3,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,26; 5,76</t>
+          <t>3,36; 5,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,26; 9,66</t>
+          <t>6,32; 9,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,79; 8,06</t>
+          <t>4,89; 8,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,09; 9,51</t>
+          <t>7,15; 10,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,45; 6,52</t>
+          <t>4,35; 6,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,46; 5,34</t>
+          <t>3,54; 5,44</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,23; 7,3</t>
+          <t>5,61; 7,55</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,14</t>
+          <t>2,02; 3,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,49</t>
+          <t>1,53; 2,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,76; 4,37</t>
+          <t>3,14; 4,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,1; 8,96</t>
+          <t>7,19; 8,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,83; 7,57</t>
+          <t>5,87; 7,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,86; 8,11</t>
+          <t>7,28; 8,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,83; 5,95</t>
+          <t>4,79; 5,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,94; 4,91</t>
+          <t>3,92; 4,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,81; 6,15</t>
+          <t>5,43; 6,47</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35765</t>
+          <t>38611</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45787</t>
+          <t>49974</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>81553</t>
+          <t>88586</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8310; 23156</t>
+          <t>7924; 23106</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6722; 21740</t>
+          <t>6722; 20596</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25671; 50130</t>
+          <t>27803; 52533</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49482; 79923</t>
+          <t>48589; 79151</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>40864; 70773</t>
+          <t>39901; 69619</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35239; 57467</t>
+          <t>40408; 60777</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>61275; 95350</t>
+          <t>62752; 95641</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>50944; 81757</t>
+          <t>51751; 84275</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>67374; 99841</t>
+          <t>73972; 109079</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25329</t>
+          <t>25924</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69318</t>
+          <t>76288</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>94647</t>
+          <t>102212</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18185; 42192</t>
+          <t>19071; 40811</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9624; 26151</t>
+          <t>10099; 25747</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12284; 39686</t>
+          <t>17239; 37537</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>67428; 105326</t>
+          <t>66747; 102708</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>47306; 80991</t>
+          <t>48726; 81669</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>57171; 83692</t>
+          <t>63189; 90251</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>92969; 136389</t>
+          <t>92331; 135689</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>64932; 100113</t>
+          <t>62722; 100730</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>64016; 115546</t>
+          <t>86036; 120921</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24135</t>
+          <t>27129</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67776</t>
+          <t>78086</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>91911</t>
+          <t>105215</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8337; 27906</t>
+          <t>8597; 29286</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11067; 28919</t>
+          <t>11033; 29686</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14997; 38443</t>
+          <t>17853; 42876</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>42401; 72264</t>
+          <t>43415; 73330</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>40674; 70819</t>
+          <t>39374; 68618</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31361; 93173</t>
+          <t>64160; 93570</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>57891; 91943</t>
+          <t>56245; 91347</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>56315; 89893</t>
+          <t>55651; 88594</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>60923; 115249</t>
+          <t>86804; 126914</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>40573</t>
+          <t>43553</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85550</t>
+          <t>94982</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>126123</t>
+          <t>138535</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17270; 39142</t>
+          <t>17067; 38006</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12923; 30822</t>
+          <t>12765; 29735</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30176; 53410</t>
+          <t>33289; 58692</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>65657; 101308</t>
+          <t>66297; 102023</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>50043; 84111</t>
+          <t>51074; 85720</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>66696; 104138</t>
+          <t>79962; 112912</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>88828; 130126</t>
+          <t>86747; 131670</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>68464; 105742</t>
+          <t>70048; 107717</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>105713; 147662</t>
+          <t>118268; 159280</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>125802</t>
+          <t>135218</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>268431</t>
+          <t>299330</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>394233</t>
+          <t>434548</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>67656; 107473</t>
+          <t>69133; 108333</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>51745; 84366</t>
+          <t>51778; 86034</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>95568; 151131</t>
+          <t>110878; 160747</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>251793; 317833</t>
+          <t>255069; 317908</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>206790; 268244</t>
+          <t>207921; 270549</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>217540; 301198</t>
+          <t>272183; 328950</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>336930; 414637</t>
+          <t>334280; 407596</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>273416; 340593</t>
+          <t>271816; 345097</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>345309; 440752</t>
+          <t>394765; 470025</t>
         </is>
       </c>
     </row>
